--- a/food_beverage_order_forms/018_frozen_beverage_shop_payment_plan_enrollment--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/018_frozen_beverage_shop_payment_plan_enrollment--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_interested'}</t>
+          <t>not_interested</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not Interested'}</t>
+          <t>Not Interested</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Failed'}</t>
+          <t>Failed</t>
         </is>
       </c>
     </row>
